--- a/BRE03D.xlsx
+++ b/BRE03D.xlsx
@@ -202,10 +202,10 @@
     <t>SOYJOY CKLT ALMND 30</t>
   </si>
   <si>
-    <t>20128818</t>
-  </si>
-  <si>
-    <t>SOYJOY MOCHACHOC 30G</t>
+    <t>20030646</t>
+  </si>
+  <si>
+    <t>SOYJOY STRAWBERRY 30</t>
   </si>
   <si>
     <t>20097488</t>
